--- a/testdata/EmpDetailsMigrationData.xlsx
+++ b/testdata/EmpDetailsMigrationData.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Nationality</t>
   </si>
   <si>
-    <t>EMPTEST012</t>
+    <t>GWP0052</t>
   </si>
   <si>
     <t xml:space="preserve">GWL EMP - </t>
@@ -50,16 +50,13 @@
     <t>AUTOMATION</t>
   </si>
   <si>
-    <t>EMPTEST013</t>
+    <t>104</t>
   </si>
   <si>
-    <t>INDN</t>
+    <t>GWP0053</t>
   </si>
   <si>
-    <t>EMPTEST014</t>
-  </si>
-  <si>
-    <t>IND</t>
+    <t>GWP0054</t>
   </si>
 </sst>
 </file>
@@ -72,7 +69,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,9 +89,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF004153"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -568,137 +570,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,7 +708,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -717,7 +720,7 @@
     <cellStyle name="Percent" xfId="3" builtinId="5"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
     <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
@@ -1269,13 +1272,13 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2">
-        <v>104</v>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
+      <c r="A3" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
@@ -1284,11 +1287,11 @@
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1298,10 +1301,14 @@
         <v>6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A3" r:id="rId1" location="EMP_SHIFT_TYPE#,00001,00001" display="GWP0053"/>
+    <hyperlink ref="A4" r:id="rId1" location="EMP_SHIFT_TYPE#,00001,00001" display="GWP0054"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/testdata/EmpDetailsMigrationData.xlsx
+++ b/testdata/EmpDetailsMigrationData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6920"/>
+    <workbookView windowWidth="13860" windowHeight="6920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Emp. ID</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>104</t>
-  </si>
-  <si>
-    <t>GWP0053</t>
   </si>
   <si>
     <t>GWP0054</t>
@@ -1245,8 +1242,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
@@ -1290,24 +1287,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" location="EMP_SHIFT_TYPE#,00001,00001" display="GWP0053"/>
-    <hyperlink ref="A4" r:id="rId1" location="EMP_SHIFT_TYPE#,00001,00001" display="GWP0054"/>
+    <hyperlink ref="A3" r:id="rId1" location="EMP_SHIFT_TYPE#,00001,00001" display="GWP0054"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
